--- a/Result/profitability/1707.xlsx
+++ b/Result/profitability/1707.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.91125</v>
+        <v>1.75625</v>
       </c>
       <c r="N2" t="n">
-        <v>70.50624999999999</v>
+        <v>69.88375000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.37</v>
       </c>
       <c r="M3" t="n">
-        <v>1.60625</v>
+        <v>1.425</v>
       </c>
       <c r="N3" t="n">
-        <v>65.64</v>
+        <v>64.99375000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>1.26875</v>
+        <v>1.29</v>
       </c>
       <c r="N4" t="n">
-        <v>60.595</v>
+        <v>60.58</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.52</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15875</v>
+        <v>1.1275</v>
       </c>
       <c r="N5" t="n">
-        <v>56.2225</v>
+        <v>55.815</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9675</v>
+        <v>0.91375</v>
       </c>
       <c r="N6" t="n">
-        <v>51.53875</v>
+        <v>51.47875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.74</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.63125</v>
       </c>
       <c r="N7" t="n">
-        <v>47.74125</v>
+        <v>47.32625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.74</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5275</v>
+        <v>0.57625</v>
       </c>
       <c r="N8" t="n">
-        <v>42.695</v>
+        <v>43.13</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>0.52375</v>
+        <v>0.5237499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>54.92625</v>
@@ -1645,10 +1645,10 @@
         <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0.57875</v>
+        <v>0.5787500000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>60.64875000000001</v>
+        <v>60.64875</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.82</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6349999999999999</v>
+        <v>0.635</v>
       </c>
       <c r="N11" t="n">
         <v>66.37375</v>
@@ -1902,7 +1902,7 @@
         <v>0.69375</v>
       </c>
       <c r="N12" t="n">
-        <v>72.1675</v>
+        <v>72.16749999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.7749999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>77.80000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2414</v>
+      </c>
+      <c r="D75" t="n">
+        <v>648</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1766</v>
+      </c>
+      <c r="F75" t="n">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>413</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.12%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>32</v>
+      </c>
+      <c r="J75" t="n">
+        <v>446</v>
+      </c>
+      <c r="K75" t="n">
+        <v>232</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>74.88124999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3900000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3305084745762714</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.480000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0499497631692265</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1373626373626373</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.259999999999991</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.04266457269990831</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
